--- a/base_datas/mediana_porte_detalhamento.xlsx
+++ b/base_datas/mediana_porte_detalhamento.xlsx
@@ -603,25 +603,25 @@
         </is>
       </c>
       <c r="B2">
-        <v>395.9212935291775</v>
+        <v>395.7365148106487</v>
       </c>
       <c r="C2">
-        <v>90.60633427287272</v>
+        <v>90.5289818796883</v>
       </c>
       <c r="D2">
-        <v>5563.086162420382</v>
+        <v>5562.991006947415</v>
       </c>
       <c r="E2">
-        <v>162.8730283490829</v>
+        <v>162.8220239550086</v>
       </c>
       <c r="F2">
-        <v>367.6141952724325</v>
+        <v>367.4774930246978</v>
       </c>
       <c r="G2">
-        <v>23.41674957301452</v>
+        <v>23.41248111693752</v>
       </c>
       <c r="H2">
-        <v>2.775689465983906</v>
+        <v>2.670883303912678</v>
       </c>
       <c r="I2">
         <v>181.8157958298182</v>
@@ -630,22 +630,22 @@
         <v>52.42899288848805</v>
       </c>
       <c r="K2">
-        <v>6.708029476546992E-15</v>
+        <v>6.63826890727803E-15</v>
       </c>
       <c r="L2">
-        <v>3270.892228474958</v>
+        <v>3270.801315593141</v>
       </c>
       <c r="M2">
-        <v>1094.482407120743</v>
+        <v>1095.548534624506</v>
       </c>
       <c r="N2">
-        <v>950.5581563882978</v>
+        <v>950.1951184201749</v>
       </c>
       <c r="O2">
-        <v>93.60521901051308</v>
+        <v>93.55897630190921</v>
       </c>
       <c r="P2">
-        <v>11.9085036063179</v>
+        <v>11.90673383511764</v>
       </c>
       <c r="Q2">
         <v>0.5190509005481597</v>
@@ -654,28 +654,28 @@
         <v>5.453566542879083</v>
       </c>
       <c r="S2">
-        <v>24.19251288659726</v>
+        <v>24.19219621547538</v>
       </c>
       <c r="T2">
-        <v>23.37024884532001</v>
+        <v>23.27963286530583</v>
       </c>
       <c r="U2">
-        <v>23.36505748454561</v>
+        <v>23.13617056077316</v>
       </c>
       <c r="V2">
-        <v>136.4826802753956</v>
+        <v>136.2654533331785</v>
       </c>
       <c r="W2">
-        <v>147.2139049796272</v>
+        <v>147.1399631837307</v>
       </c>
       <c r="Z2">
-        <v>1.240176007530998E-14</v>
+        <v>1.230903481109194E-14</v>
       </c>
       <c r="AA2">
-        <v>11.43544011849344</v>
+        <v>11.41643023979309</v>
       </c>
       <c r="AB2">
-        <v>13.48756383247662</v>
+        <v>13.45249959709493</v>
       </c>
       <c r="AC2">
         <v>1.048650641961176E-16</v>
@@ -690,28 +690,28 @@
         <v>31.60231132377562</v>
       </c>
       <c r="AG2">
-        <v>0.236929932735426</v>
+        <v>0.220488290914402</v>
       </c>
       <c r="AH2">
-        <v>2043.212149674385</v>
+        <v>2043.469304140127</v>
       </c>
       <c r="AJ2">
-        <v>41.06894641071767</v>
+        <v>41.06420902489626</v>
       </c>
       <c r="AK2">
-        <v>541.2672697607356</v>
+        <v>542.6236159122085</v>
       </c>
       <c r="AL2">
-        <v>116.4710996965987</v>
+        <v>116.5230741246334</v>
       </c>
       <c r="AM2">
         <v>351.0741546905467</v>
       </c>
       <c r="AN2">
-        <v>28.43313020013492</v>
+        <v>28.43228445163788</v>
       </c>
       <c r="AO2">
-        <v>58.02238038167261</v>
+        <v>57.99858219884003</v>
       </c>
       <c r="AP2">
         <v>759.6733585455554</v>
@@ -726,10 +726,10 @@
         <v>7.648910105205279</v>
       </c>
       <c r="AT2">
-        <v>3.425414449974258</v>
+        <v>3.412568151510767</v>
       </c>
       <c r="AU2">
-        <v>75.45179839391378</v>
+        <v>75.50097195198097</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -751,7 +751,7 @@
         <v>3582.600684871743</v>
       </c>
       <c r="E3">
-        <v>360.5050999086694</v>
+        <v>360.5050999086696</v>
       </c>
       <c r="F3">
         <v>889.0500761645483</v>
@@ -881,49 +881,49 @@
         </is>
       </c>
       <c r="B4">
-        <v>492.2404947409619</v>
+        <v>494.7866184879729</v>
       </c>
       <c r="C4">
-        <v>117.7607563652839</v>
+        <v>118.236527948468</v>
       </c>
       <c r="D4">
-        <v>4732.682167833893</v>
+        <v>4740.735303300828</v>
       </c>
       <c r="E4">
-        <v>185.5290676561439</v>
+        <v>185.5559520644512</v>
       </c>
       <c r="F4">
-        <v>443.9114555415077</v>
+        <v>445.4527064276077</v>
       </c>
       <c r="G4">
-        <v>33.07247701048439</v>
+        <v>33.84048471353944</v>
       </c>
       <c r="H4">
         <v>1.246905648590856</v>
       </c>
       <c r="I4">
-        <v>176.9292844302618</v>
+        <v>177.4062863028749</v>
       </c>
       <c r="J4">
-        <v>63.3604617162261</v>
+        <v>63.50224311461341</v>
       </c>
       <c r="K4">
-        <v>7.273684587749755E-15</v>
+        <v>7.216429091333054E-15</v>
       </c>
       <c r="L4">
-        <v>2673.545560235485</v>
+        <v>2678.471987315011</v>
       </c>
       <c r="M4">
-        <v>1027.734927043608</v>
+        <v>1039.148800757915</v>
       </c>
       <c r="N4">
-        <v>911.5304557873502</v>
+        <v>912.6822823358953</v>
       </c>
       <c r="O4">
-        <v>90.86208651370625</v>
+        <v>90.96113455552447</v>
       </c>
       <c r="P4">
-        <v>12.82108592561663</v>
+        <v>12.84538616445018</v>
       </c>
       <c r="Q4">
         <v>0.7161315062671668</v>
@@ -932,31 +932,31 @@
         <v>1.074815625777557</v>
       </c>
       <c r="S4">
-        <v>35.08755998828106</v>
+        <v>35.14426451207667</v>
       </c>
       <c r="T4">
-        <v>49.17607677666932</v>
+        <v>50.90144397533813</v>
       </c>
       <c r="U4">
-        <v>29.40178799801884</v>
+        <v>29.40421659426171</v>
       </c>
       <c r="V4">
-        <v>174.3930067069952</v>
+        <v>174.7553375191012</v>
       </c>
       <c r="W4">
-        <v>154.3325995392204</v>
+        <v>155.3536429731037</v>
       </c>
       <c r="Z4">
-        <v>1.632490666555805E-14</v>
+        <v>1.638671525170635E-14</v>
       </c>
       <c r="AA4">
-        <v>16.74074845574643</v>
+        <v>16.86503227671982</v>
       </c>
       <c r="AB4">
-        <v>14.31328984684339</v>
+        <v>14.37989422662089</v>
       </c>
       <c r="AC4">
-        <v>1.912177556460683E-16</v>
+        <v>2.079523485619969E-16</v>
       </c>
       <c r="AD4">
         <v>0.6588549136336986</v>
@@ -971,37 +971,37 @@
         <v>0.1329977263740609</v>
       </c>
       <c r="AH4">
-        <v>1467.741144857041</v>
+        <v>1468.572095527262</v>
       </c>
       <c r="AJ4">
-        <v>31.67430216102505</v>
+        <v>31.68707487952051</v>
       </c>
       <c r="AK4">
-        <v>515.5558512826483</v>
+        <v>516.5100204290092</v>
       </c>
       <c r="AL4">
-        <v>111.6368892326615</v>
+        <v>111.6992458459507</v>
       </c>
       <c r="AM4">
-        <v>371.5033769081213</v>
+        <v>375.4044398108167</v>
       </c>
       <c r="AN4">
-        <v>23.85005407444833</v>
+        <v>23.89661564773121</v>
       </c>
       <c r="AO4">
-        <v>44.80826046455707</v>
+        <v>44.98628476821192</v>
       </c>
       <c r="AP4">
-        <v>638.5754174162465</v>
+        <v>641.1955208709794</v>
       </c>
       <c r="AQ4">
-        <v>98.51454690879596</v>
+        <v>98.87028445153794</v>
       </c>
       <c r="AR4">
         <v>42.64297852264453</v>
       </c>
       <c r="AS4">
-        <v>6.297758391251802</v>
+        <v>6.330948187603035</v>
       </c>
       <c r="AT4">
         <v>3.556457289773483</v>
@@ -1029,7 +1029,7 @@
         <v>3230.766258960618</v>
       </c>
       <c r="E5">
-        <v>447.8141805690632</v>
+        <v>447.814180569063</v>
       </c>
       <c r="F5">
         <v>1183.732105723766</v>
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>445.9319608102741</v>
+        <v>451.313247341473</v>
       </c>
       <c r="C6">
-        <v>78.27886416268849</v>
+        <v>78.31836923954914</v>
       </c>
       <c r="D6">
-        <v>6481.426244135848</v>
+        <v>6482.34433778626</v>
       </c>
       <c r="E6">
-        <v>198.1832109233268</v>
+        <v>198.183210923327</v>
       </c>
       <c r="F6">
-        <v>402.1799409882482</v>
+        <v>402.2387205034085</v>
       </c>
       <c r="G6">
         <v>26.35809438470729</v>
@@ -1183,22 +1183,22 @@
         <v>213.4584245973646</v>
       </c>
       <c r="J6">
-        <v>51.42057406330687</v>
+        <v>51.43134253316217</v>
       </c>
       <c r="K6">
         <v>2.830234479193998E-15</v>
       </c>
       <c r="L6">
-        <v>3775.11480058472</v>
+        <v>3775.277553276719</v>
       </c>
       <c r="M6">
-        <v>1601.900283185841</v>
+        <v>1603.530704810154</v>
       </c>
       <c r="N6">
-        <v>950.1406652551589</v>
+        <v>950.4915549181308</v>
       </c>
       <c r="O6">
-        <v>124.7384472413289</v>
+        <v>125.2298467635403</v>
       </c>
       <c r="P6">
         <v>16.19710613349369</v>
@@ -1210,25 +1210,25 @@
         <v>6.422680679349327</v>
       </c>
       <c r="S6">
-        <v>19.4904761904756</v>
+        <v>19.60228418399468</v>
       </c>
       <c r="T6">
-        <v>34.18051474628494</v>
+        <v>34.32556994818653</v>
       </c>
       <c r="U6">
-        <v>42.11274395706574</v>
+        <v>42.07146401548478</v>
       </c>
       <c r="V6">
-        <v>134.308799914295</v>
+        <v>134.3537074271646</v>
       </c>
       <c r="W6">
-        <v>146.2596571789049</v>
+        <v>146.3780445639647</v>
       </c>
       <c r="Z6">
-        <v>1.338260970536094E-14</v>
+        <v>1.343376528514513E-14</v>
       </c>
       <c r="AA6">
-        <v>10.35181432325125</v>
+        <v>10.36343395623702</v>
       </c>
       <c r="AB6">
         <v>16.3395336723304</v>
@@ -1249,43 +1249,43 @@
         <v>0.3634059767714994</v>
       </c>
       <c r="AH6">
-        <v>2530.735674617337</v>
+        <v>2531.821693250237</v>
       </c>
       <c r="AJ6">
         <v>52.07491445427728</v>
       </c>
       <c r="AK6">
-        <v>542.976066324374</v>
+        <v>543.9228603435399</v>
       </c>
       <c r="AL6">
-        <v>109.6256099033816</v>
+        <v>109.6264823064002</v>
       </c>
       <c r="AM6">
-        <v>214.6332325581395</v>
+        <v>215.5669293786686</v>
       </c>
       <c r="AN6">
-        <v>36.673764832331</v>
+        <v>36.68797587131367</v>
       </c>
       <c r="AO6">
-        <v>67.85984163373516</v>
+        <v>68.05639688249396</v>
       </c>
       <c r="AP6">
-        <v>1153.518123212063</v>
+        <v>1153.566096611391</v>
       </c>
       <c r="AQ6">
-        <v>140.8569552956586</v>
+        <v>141.0729637256455</v>
       </c>
       <c r="AR6">
-        <v>75.83103065107619</v>
+        <v>75.9719230197652</v>
       </c>
       <c r="AS6">
         <v>10.32303576391954</v>
       </c>
       <c r="AT6">
-        <v>3.768033926016759</v>
+        <v>3.746393620516443</v>
       </c>
       <c r="AU6">
-        <v>113.6042090784041</v>
+        <v>113.6053730661921</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1307,7 +1307,7 @@
         <v>4094.032462370825</v>
       </c>
       <c r="E7">
-        <v>273.9346762967269</v>
+        <v>273.9346762967268</v>
       </c>
       <c r="F7">
         <v>736.3313570746276</v>
@@ -1446,7 +1446,7 @@
         <v>2876.921237293286</v>
       </c>
       <c r="E8">
-        <v>366.5021721526072</v>
+        <v>366.5021721526074</v>
       </c>
       <c r="F8">
         <v>1753.010383187979</v>
@@ -1594,7 +1594,7 @@
         <v>10169.97456161715</v>
       </c>
       <c r="E9">
-        <v>311.166354556804</v>
+        <v>311.566927278402</v>
       </c>
       <c r="F9">
         <v>513.4506457242583</v>
